--- a/data/case15_mask.xlsx
+++ b/data/case15_mask.xlsx
@@ -5440,7 +5440,7 @@
     </row>
     <row r="1003">
       <c r="A1003" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1004">
@@ -6560,17 +6560,17 @@
     </row>
     <row r="1227">
       <c r="A1227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1230">
@@ -6715,7 +6715,7 @@
     </row>
     <row r="1258">
       <c r="A1258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1259">
@@ -6735,7 +6735,7 @@
     </row>
     <row r="1262">
       <c r="A1262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1263">
@@ -18260,17 +18260,17 @@
     </row>
     <row r="3567">
       <c r="A3567" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3568">
       <c r="A3568" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3569">
       <c r="A3569" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3570">
@@ -18365,7 +18365,7 @@
     </row>
     <row r="3588">
       <c r="A3588" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3589">
@@ -20025,7 +20025,7 @@
     </row>
     <row r="3920">
       <c r="A3920" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3921">
@@ -27115,12 +27115,12 @@
     </row>
     <row r="5338">
       <c r="A5338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5339">
       <c r="A5339" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5340">
@@ -38350,12 +38350,12 @@
     </row>
     <row r="7585">
       <c r="A7585" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7586">
       <c r="A7586" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7587">
@@ -38390,7 +38390,7 @@
     </row>
     <row r="7593">
       <c r="A7593" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7594">
@@ -38425,7 +38425,7 @@
     </row>
     <row r="7600">
       <c r="A7600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7601">
@@ -41880,7 +41880,7 @@
     </row>
     <row r="8291">
       <c r="A8291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8292">
@@ -41900,7 +41900,7 @@
     </row>
     <row r="8295">
       <c r="A8295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8296">
@@ -41920,12 +41920,12 @@
     </row>
     <row r="8299">
       <c r="A8299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8300">
       <c r="A8300" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8301">
@@ -61545,7 +61545,7 @@
     </row>
     <row r="12224">
       <c r="A12224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12225">
@@ -63435,7 +63435,7 @@
     </row>
     <row r="12602">
       <c r="A12602" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12603">
@@ -73830,7 +73830,7 @@
     </row>
     <row r="14681">
       <c r="A14681" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14682">
@@ -76125,27 +76125,27 @@
     </row>
     <row r="15140">
       <c r="A15140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15141">
       <c r="A15141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15142">
       <c r="A15142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15143">
       <c r="A15143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15144">
       <c r="A15144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15145">
@@ -76155,7 +76155,7 @@
     </row>
     <row r="15146">
       <c r="A15146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15147">
@@ -76200,7 +76200,7 @@
     </row>
     <row r="15155">
       <c r="A15155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15156">
@@ -76215,7 +76215,7 @@
     </row>
     <row r="15158">
       <c r="A15158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15159">
@@ -76235,7 +76235,7 @@
     </row>
     <row r="15162">
       <c r="A15162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15163">
@@ -76315,7 +76315,7 @@
     </row>
     <row r="15178">
       <c r="A15178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15179">
@@ -80220,7 +80220,7 @@
     </row>
     <row r="15959">
       <c r="A15959" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15960">
@@ -91605,7 +91605,7 @@
     </row>
     <row r="18236">
       <c r="A18236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18237">
@@ -96605,12 +96605,12 @@
     </row>
     <row r="19236">
       <c r="A19236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19237">
       <c r="A19237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19238">
@@ -96630,7 +96630,7 @@
     </row>
     <row r="19241">
       <c r="A19241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19242">
@@ -96640,7 +96640,7 @@
     </row>
     <row r="19243">
       <c r="A19243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19244">
@@ -100695,12 +100695,12 @@
     </row>
     <row r="20054">
       <c r="A20054" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20055">
       <c r="A20055" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20056">
